--- a/SVV_Balaji_Weekly_Project_Report.xlsx
+++ b/SVV_Balaji_Weekly_Project_Report.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="287">
   <si>
     <t xml:space="preserve">SVV BALAJI - PROJECT GANTT CHART</t>
   </si>
@@ -547,7 +547,7 @@
     <t xml:space="preserve">Yellow rows are B2C activities added by Decision 1 - not in the signed scope of work.</t>
   </si>
   <si>
-    <t xml:space="preserve">WEEKLY PROGRESS REPORT - WEEK 2, UPDATED 13-AUG-2026</t>
+    <t xml:space="preserve">WEEKLY PROGRESS REPORT - WEEK 2, UPDATED 14-AUG-2026</t>
   </si>
   <si>
     <t xml:space="preserve">Planned % (this wk)</t>
@@ -607,6 +607,9 @@
     <t xml:space="preserve">Live demo: full trace from finished pack to farmer</t>
   </si>
   <si>
+    <t xml:space="preserve">Complete ahead of plan. Multigrain production unblocked and enforcing as of 14-Aug (A-05): blend ratio checked against the approved recipe on every run.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sales &amp; order fulfilment (B2B), dispatch &amp; delivery</t>
   </si>
   <si>
@@ -652,7 +655,7 @@
     <t xml:space="preserve">Live screens: products with B2B/B2C pricing, recipes with versioning and approval, cleaning &amp; grading, production batches with per-batch consumption, quality inspections across all three stages, finished goods with QA release, label printing and stock-in</t>
   </si>
   <si>
-    <t xml:space="preserve">Complete - 8 weeks ahead of baseline. Panel is now 22 of 25 screens. Recipe composition rules and quality gates are enforced in the forms, not discovered through server errors. Multigrain production remains disabled pending Decision A-05. Pending manual test.</t>
+    <t xml:space="preserve">Complete - 8 weeks ahead of baseline. Panel is 22 of 25 screens. Recipe composition rules and quality gates are enforced in the forms, not discovered through server errors. Multigrain production live as of 14-Aug with a blend worksheet showing the required quantity per grain. Pending manual test.</t>
   </si>
   <si>
     <t xml:space="preserve">Live screen: farm-to-fork trace - a finished-goods batch number resolves to the production run, recipe version, quality checks and the farmers behind it</t>
@@ -700,7 +703,7 @@
     <t xml:space="preserve">Frontend is running well ahead of baseline: WS2.1, WS2.3 and WS2.4 are complete and WS2.2 and WS2.6 are underway, between 4 and 8 weeks earlier than the proposed schedule. The admin panel now covers 22 of its 25 screens; only the sales screens (customers, price lists, orders) remain, and those are held pending A-13.</t>
   </si>
   <si>
-    <t xml:space="preserve">No activity is DELAYED. WS4.1 remains blocked on Decision 3 (A-04). A-12 (pagination and response envelope) reached its 13-Aug target without landing - 22 panel screens are now built against the current shape and absorb it through an adapter, so nothing is blocked, but the change is now larger than it was on 11-Aug. A-05 (multigrain) is now visible in the product: multigrain recipes can be created but not produced.</t>
+    <t xml:space="preserve">No activity is DELAYED. A-05 (multigrain) CLOSED 14-Aug - blended production is in scope, the feature flag has been removed and the blend ratio is now enforced at production time rather than only at recipe approval. WS4.1 remains blocked on Decision 3 (A-04). A-12 (pagination and response envelope) reached its 13-Aug target without landing; 22 panel screens absorb it through an adapter, so nothing is blocked, but the change is now larger than it was on 11-Aug.</t>
   </si>
   <si>
     <t xml:space="preserve">CONSOLIDATED ACTION TRACKER</t>
@@ -793,7 +796,7 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">Now has a visible cost in the panel: WS2.4 accepts multigrain recipes because the API does, then disables the production button for them with the reason on screen. That path is incomplete for any demonstration until this is decided.</t>
+    <t xml:space="preserve">CLOSED 14-Aug-2026. Multigrain (blended) production confirmed in scope. The MULTIGRAIN_ENABLED flag has been removed rather than switched on, so a stale .env cannot silently re-block it. Blend ratio is now enforced at production time: a run whose mix drifts more than 0.5 percentage points from the approved recipe, or omits one of its grains, is refused. The admin panel shows the required quantity per grain and a live share as the operator selects batches.</t>
   </si>
   <si>
     <t xml:space="preserve">A-06</t>
@@ -6780,7 +6783,7 @@
         <v>193</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6788,7 +6791,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>0.05</v>
@@ -6804,10 +6807,10 @@
         <v>182</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6815,7 +6818,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>0</v>
@@ -6834,7 +6837,7 @@
         <v>165</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6842,7 +6845,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0</v>
@@ -6861,7 +6864,7 @@
         <v>165</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6869,7 +6872,7 @@
         <v>57</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>0</v>
@@ -6885,10 +6888,10 @@
         <v>186</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6912,10 +6915,10 @@
         <v>186</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6939,10 +6942,10 @@
         <v>186</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6966,10 +6969,10 @@
         <v>186</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6993,10 +6996,10 @@
         <v>186</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7004,7 +7007,7 @@
         <v>80</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>0</v>
@@ -7023,7 +7026,7 @@
         <v>165</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7031,7 +7034,7 @@
         <v>84</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>0</v>
@@ -7050,7 +7053,7 @@
         <v>165</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7058,7 +7061,7 @@
         <v>91</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>0</v>
@@ -7077,7 +7080,7 @@
         <v>165</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7085,7 +7088,7 @@
         <v>93</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0</v>
@@ -7104,7 +7107,7 @@
         <v>165</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7112,7 +7115,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>0.45</v>
@@ -7128,16 +7131,16 @@
         <v>186</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D22" s="32" t="n">
         <f aca="false">'2. Schedule Baseline'!H45</f>
@@ -7146,12 +7149,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -7189,7 +7192,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7202,7 +7205,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7215,247 +7218,247 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C5" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E5" s="35" t="n">
         <v>46248</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G5" s="15" t="n">
         <f aca="true">IF(F5="Closed","",TODAY()-C5)</f>
         <v>6</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C6" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" s="35" t="n">
         <v>46246</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G6" s="15" t="str">
         <f aca="true">IF(F6="Closed","",TODAY()-C6)</f>
         <v/>
       </c>
       <c r="H6" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C7" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E7" s="35" t="n">
         <v>46248</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G7" s="15" t="str">
         <f aca="true">IF(F7="Closed","",TODAY()-C7)</f>
         <v/>
       </c>
       <c r="H7" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C8" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E8" s="35" t="n">
         <v>46248</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G8" s="15" t="n">
         <f aca="true">IF(F8="Closed","",TODAY()-C8)</f>
         <v>6</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E9" s="35" t="n">
         <v>46248</v>
       </c>
-      <c r="F9" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="G9" s="15" t="n">
+      <c r="F9" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" s="15" t="str">
         <f aca="true">IF(F9="Closed","",TODAY()-C9)</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="H9" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C10" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E10" s="35" t="n">
         <v>46262</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G10" s="15" t="n">
         <f aca="true">IF(F10="Closed","",TODAY()-C10)</f>
         <v>6</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E11" s="35" t="n">
         <v>46262</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G11" s="15" t="n">
         <f aca="true">IF(F11="Closed","",TODAY()-C11)</f>
         <v>6</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C12" s="35" t="n">
         <v>46241</v>
@@ -7467,179 +7470,179 @@
         <v>46255</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G12" s="15" t="n">
         <f aca="true">IF(F12="Closed","",TODAY()-C12)</f>
         <v>6</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C13" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>46255</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G13" s="15" t="n">
         <f aca="true">IF(F13="Closed","",TODAY()-C13)</f>
         <v>6</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C14" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E14" s="35" t="n">
         <v>46252</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G14" s="15" t="n">
         <f aca="true">IF(F14="Closed","",TODAY()-C14)</f>
         <v>2</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C15" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E15" s="35" t="n">
         <v>46252</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G15" s="15" t="n">
         <f aca="true">IF(F15="Closed","",TODAY()-C15)</f>
         <v>2</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C16" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E16" s="35" t="n">
         <v>46247</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="true">IF(F16="Closed","",TODAY()-C16)</f>
         <v>2</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C17" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E17" s="35" t="n">
         <v>46249</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="true">IF(F17="Closed","",TODAY()-C17)</f>
         <v>2</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C19" s="30" t="n">
         <f aca="false">COUNTIF(F5:F17,"Open")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C20" s="30" t="n">
         <f aca="false">COUNTIFS(F5:F17,"Open",H5:H17,"Critical")</f>
@@ -7648,11 +7651,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C21" s="30" t="n">
         <f aca="false">COUNTIF(F5:F17,"Closed")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/SVV_Balaji_Weekly_Project_Report.xlsx
+++ b/SVV_Balaji_Weekly_Project_Report.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="288">
   <si>
     <t xml:space="preserve">SVV BALAJI - PROJECT GANTT CHART</t>
   </si>
@@ -283,396 +283,396 @@
     <t xml:space="preserve">Cloud object storage (photos, documents, video)</t>
   </si>
   <si>
+    <t xml:space="preserve">WS4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp Business API (via BSP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS4.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS / OTP gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS4.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GST e-invoicing (IRN/IRP) &amp; e-way bill via GST Suvidha Provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment gateway - Razorpay (B2C confirmed, was on hold)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUALITY, DEPLOYMENT &amp; HANDOVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated test suite &amp; continuous integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staging environment &amp; deployment pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data migration (existing customer &amp; product masters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User acceptance testing (UAT) with SVV Balaji - B2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backups, monitoring &amp; disaster recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training &amp; handover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go-live &amp; hypercare - B2B launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS5.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2C UAT &amp; consumer channel launch  [NEW - Decision 1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEGEND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In progress / planned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocked - awaiting client decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2C scope - conditional on A-10 (cost &amp; timeline agreement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red vertical line = current reporting week (w/c 11-Aug-2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bars are formula-driven: edit the Start / Finish week columns and the chart updates automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVV BALAJI - REVISED ACTIVITY-WISE SCHEDULE BASELINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revised 11-Aug-2026. Decision 1 (both B2B and B2C sales channels with separate pricing) adds four activities beyond the signed scope of work: WS1.6, WS1.7, WS3.5 and WS5.8, plus activation of WS4.5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weeks are numbered from Week 1 commencing 04-Aug-2026. B2C activities extend the programme to Week 21 and are conditional on written agreement of cost and timeline (action A-10). The B2B launch remains at Week 18.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workstream / Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD Ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned Start (Wk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned Finish (Wk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 5,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 7-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 13-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 18-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 24-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 24-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 29-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 31-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 33-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 6-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 16-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 27-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 29-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 28,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL WEIGHTED PROJECT COMPLETION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight validation (must equal 100%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight % reflects estimated share of total project effort, revised for the added B2C scope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow rows are B2C activities added by Decision 1 - not in the signed scope of work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEEKLY PROGRESS REPORT - WEEK 2, UPDATED 14-AUG-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned % (this wk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual % (this wk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Deliverable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foundation: auth, roles, permissions, CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swagger API docs; 50 automated tests passing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete and verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farm sourcing &amp; farmer traceability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahead of schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live demo: farmer approval issues SVV-2026-NNNNNN code + QR/barcode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete. Training records confirmed as executive-entered - no farmer app required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procurement, batching, warehouse &amp; inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live demo: RM-YYYYMMDD-NNN batch generation; inventory ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete ahead of plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processing, recipes, QA, packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live demo: full trace from finished pack to farmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete ahead of plan. Multigrain production unblocked and enforcing as of 14-Aug (A-05): blend ratio checked against the approved recipe on every run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales &amp; order fulfilment (B2B), dispatch &amp; delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channel-aware order model in design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNBLOCKED 11-Aug by Decision 1. Building channel-aware from the start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channel pricing engine (B2B / B2C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW activity from Decision 1. Dated price lists per channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer (B2C) commerce APIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW - not in signed SOW. Held pending A-10 cost &amp; timeline agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin panel scaffolding, auth, role-based navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live panel: sign-in, session refresh, role-filtered menu across 25 screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete. Also added the missing /auth/refresh, /auth/logout and /auth/me endpoints, without which no client could hold a session beyond 15 minutes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live screens: branches, users, farmers (registration, approval, QR/barcode), agreements, seed distribution, training, field visits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Started 6 weeks early. All FRD 6-12 screens built and manually tested end to end. Remaining 20% is the product &amp; channel-pricing screens added by Decision 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live screens: procurement plans, harvest inspections, collections, raw material batches with upstream trace, warehouses with per-unit occupancy, batch-wise stock (in/out/transfer/adjust) and the append-only movement ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete - 6 weeks ahead of baseline. Quality gates surfaced in the UI: only approved farmers can be inspected, only approved inspections collected, and reserved stock cannot be withdrawn. Pending manual test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live screens: products with B2B/B2C pricing, recipes with versioning and approval, cleaning &amp; grading, production batches with per-batch consumption, quality inspections across all three stages, finished goods with QA release, label printing and stock-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete - 8 weeks ahead of baseline. Panel is 22 of 25 screens. Recipe composition rules and quality gates are enforced in the forms, not discovered through server errors. Multigrain production live as of 14-Aug with a blend worksheet showing the required quantity per grain. Pending manual test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live screen: farm-to-fork trace - a finished-goods batch number resolves to the production run, recipe version, quality checks and the farmers behind it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traceability screen built early for client demonstration. Dashboards and MIS reports still to come.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer app / website (B2C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW - not in signed SOW. Held pending A-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud object storage</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blocked</t>
   </si>
   <si>
-    <t xml:space="preserve">WS4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp Business API (via BSP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS / OTP gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS4.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GST e-invoicing (IRN/IRP) &amp; e-way bill via GST Suvidha Provider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS4.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment gateway - Razorpay (B2C confirmed, was on hold)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUALITY, DEPLOYMENT &amp; HANDOVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automated test suite &amp; continuous integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staging environment &amp; deployment pipeline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data migration (existing customer &amp; product masters)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User acceptance testing (UAT) with SVV Balaji - B2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backups, monitoring &amp; disaster recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training &amp; handover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go-live &amp; hypercare - B2B launch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS5.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2C UAT &amp; consumer channel launch  [NEW - Decision 1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEGEND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In progress / planned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked - awaiting client decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2C scope - conditional on A-10 (cost &amp; timeline agreement)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red vertical line = current reporting week (w/c 11-Aug-2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bars are formula-driven: edit the Start / Finish week columns and the chart updates automatically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVV BALAJI - REVISED ACTIVITY-WISE SCHEDULE BASELINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revised 11-Aug-2026. Decision 1 (both B2B and B2C sales channels with separate pricing) adds four activities beyond the signed scope of work: WS1.6, WS1.7, WS3.5 and WS5.8, plus activation of WS4.5.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weeks are numbered from Week 1 commencing 04-Aug-2026. B2C activities extend the programme to Week 21 and are conditional on written agreement of cost and timeline (action A-10). The B2B launch remains at Week 18.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workstream / Activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD Ref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned Start (Wk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned Finish (Wk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% Complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 5,6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 7-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 13-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 18-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 24-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 24-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 29-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 31-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 33-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 6-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 16-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 27-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 29-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 28,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRD 26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL WEIGHTED PROJECT COMPLETION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight validation (must equal 100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight % reflects estimated share of total project effort, revised for the added B2C scope.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow rows are B2C activities added by Decision 1 - not in the signed scope of work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WEEKLY PROGRESS REPORT - WEEK 2, UPDATED 14-AUG-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned % (this wk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual % (this wk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence / Deliverable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foundation: auth, roles, permissions, CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On schedule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swagger API docs; 50 automated tests passing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete and verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farm sourcing &amp; farmer traceability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahead of schedule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live demo: farmer approval issues SVV-2026-NNNNNN code + QR/barcode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete. Training records confirmed as executive-entered - no farmer app required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procurement, batching, warehouse &amp; inventory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live demo: RM-YYYYMMDD-NNN batch generation; inventory ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete ahead of plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processing, recipes, QA, packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live demo: full trace from finished pack to farmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete ahead of plan. Multigrain production unblocked and enforcing as of 14-Aug (A-05): blend ratio checked against the approved recipe on every run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales &amp; order fulfilment (B2B), dispatch &amp; delivery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Channel-aware order model in design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNBLOCKED 11-Aug by Decision 1. Building channel-aware from the start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Channel pricing engine (B2B / B2C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW activity from Decision 1. Dated price lists per channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer (B2C) commerce APIs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW - not in signed SOW. Held pending A-10 cost &amp; timeline agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin panel scaffolding, auth, role-based navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live panel: sign-in, session refresh, role-filtered menu across 25 screens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete. Also added the missing /auth/refresh, /auth/logout and /auth/me endpoints, without which no client could hold a session beyond 15 minutes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live screens: branches, users, farmers (registration, approval, QR/barcode), agreements, seed distribution, training, field visits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Started 6 weeks early. All FRD 6-12 screens built and manually tested end to end. Remaining 20% is the product &amp; channel-pricing screens added by Decision 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live screens: procurement plans, harvest inspections, collections, raw material batches with upstream trace, warehouses with per-unit occupancy, batch-wise stock (in/out/transfer/adjust) and the append-only movement ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete - 6 weeks ahead of baseline. Quality gates surfaced in the UI: only approved farmers can be inspected, only approved inspections collected, and reserved stock cannot be withdrawn. Pending manual test.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live screens: products with B2B/B2C pricing, recipes with versioning and approval, cleaning &amp; grading, production batches with per-batch consumption, quality inspections across all three stages, finished goods with QA release, label printing and stock-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete - 8 weeks ahead of baseline. Panel is 22 of 25 screens. Recipe composition rules and quality gates are enforced in the forms, not discovered through server errors. Multigrain production live as of 14-Aug with a blend worksheet showing the required quantity per grain. Pending manual test.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live screen: farm-to-fork trace - a finished-goods batch number resolves to the production run, recipe version, quality checks and the farmers behind it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traceability screen built early for client demonstration. Dashboards and MIS reports still to come.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer app / website (B2C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW - not in signed SOW. Held pending A-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud object storage</t>
-  </si>
-  <si>
     <t xml:space="preserve">Still awaiting Decision 3. More urgent now B2C is confirmed</t>
   </si>
   <si>
@@ -784,7 +784,10 @@
     <t xml:space="preserve">Decision 3: approve cloud object storage provider and confirm whether QR process videos are required</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority raised from High to Critical - B2C drives media delivery volume well above internal use</t>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escalation note issued 14-Aug (SVV_Balaji_A04_Storage_Decision_Note.md), target moved to 21-Aug. NO LONGER BLOCKING: an interim Cloudinary account is in use from 14-Aug, so the field executive module and all photo capture ship on schedule. Storage sits behind a single interface in the codebase, so switching provider later is one class and one line. The open question is now ownership and permanence rather than capability - the account must be opened in SVV Balaji's name so media and billing belong to the client. Also needs a retention and access policy for farmer KYC images (Aadhaar, PAN), which shapes access control not just storage.</t>
   </si>
   <si>
     <t xml:space="preserve">A-05</t>
@@ -3985,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="H30" s="17" t="str">
         <f aca="false">IF(AND($D30&lt;&gt;"",$E30&lt;&gt;"",H$5&gt;=$D30,H$5&lt;=$E30),IF($F30&gt;=1,3,IF($G30="Blocked",2,IF($G30="Conditional",4,1))),"")</f>
@@ -4005,11 +4008,11 @@
       </c>
       <c r="L30" s="17" t="n">
         <f aca="false">IF(AND($D30&lt;&gt;"",$E30&lt;&gt;"",L$5&gt;=$D30,L$5&lt;=$E30),IF($F30&gt;=1,3,IF($G30="Blocked",2,IF($G30="Conditional",4,1))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" s="17" t="n">
         <f aca="false">IF(AND($D30&lt;&gt;"",$E30&lt;&gt;"",M$5&gt;=$D30,M$5&lt;=$E30),IF($F30&gt;=1,3,IF($G30="Blocked",2,IF($G30="Conditional",4,1))),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30" s="17" t="str">
         <f aca="false">IF(AND($D30&lt;&gt;"",$E30&lt;&gt;"",N$5&gt;=$D30,N$5&lt;=$E30),IF($F30&gt;=1,3,IF($G30="Blocked",2,IF($G30="Conditional",4,1))),"")</f>
@@ -4074,10 +4077,10 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>34</v>
@@ -4181,10 +4184,10 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="14" t="s">
         <v>89</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>34</v>
@@ -4288,10 +4291,10 @@
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>92</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>34</v>
@@ -4395,10 +4398,10 @@
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>93</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>34</v>
@@ -4502,10 +4505,10 @@
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -4536,10 +4539,10 @@
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>98</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>34</v>
@@ -4643,10 +4646,10 @@
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>100</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>34</v>
@@ -4750,10 +4753,10 @@
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>59</v>
@@ -4857,13 +4860,13 @@
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="C39" s="15" t="s">
         <v>104</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>105</v>
       </c>
       <c r="D39" s="15" t="n">
         <v>15</v>
@@ -4964,10 +4967,10 @@
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>107</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>34</v>
@@ -5071,13 +5074,13 @@
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="C41" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D41" s="15" t="n">
         <v>17</v>
@@ -5178,13 +5181,13 @@
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>111</v>
-      </c>
       <c r="C42" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D42" s="15" t="n">
         <v>18</v>
@@ -5285,13 +5288,13 @@
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>113</v>
-      </c>
       <c r="C43" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D43" s="15" t="n">
         <v>19</v>
@@ -5392,7 +5395,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5404,29 +5407,29 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="22"/>
       <c r="B47" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="23"/>
       <c r="B48" s="21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="24"/>
       <c r="B49" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -5477,7 +5480,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5490,7 +5493,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5503,7 +5506,7 @@
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5519,25 +5522,25 @@
         <v>23</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>29</v>
@@ -5566,16 +5569,16 @@
         <v>33</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>0.03</v>
@@ -5595,16 +5598,16 @@
         <v>37</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.05</v>
@@ -5624,16 +5627,16 @@
         <v>39</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>0.05</v>
@@ -5653,16 +5656,16 @@
         <v>41</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>0.06</v>
@@ -5682,16 +5685,16 @@
         <v>43</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>0.06</v>
@@ -5711,16 +5714,16 @@
         <v>46</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" s="16" t="n">
         <v>0.02</v>
@@ -5740,16 +5743,16 @@
         <v>48</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G13" s="29" t="n">
         <v>0.04</v>
@@ -5769,16 +5772,16 @@
         <v>51</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G14" s="16" t="n">
         <v>0.03</v>
@@ -5798,16 +5801,16 @@
         <v>54</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G15" s="16" t="n">
         <v>0.02</v>
@@ -5842,16 +5845,16 @@
         <v>58</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G17" s="16" t="n">
         <v>0.03</v>
@@ -5871,16 +5874,16 @@
         <v>61</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G18" s="16" t="n">
         <v>0.05</v>
@@ -5900,16 +5903,16 @@
         <v>63</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>0.04</v>
@@ -5929,16 +5932,16 @@
         <v>65</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G20" s="16" t="n">
         <v>0.04</v>
@@ -5958,16 +5961,16 @@
         <v>67</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E21" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>149</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>150</v>
       </c>
       <c r="G21" s="16" t="n">
         <v>0.03</v>
@@ -5987,16 +5990,16 @@
         <v>69</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G22" s="16" t="n">
         <v>0.03</v>
@@ -6031,16 +6034,16 @@
         <v>73</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E24" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>149</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>150</v>
       </c>
       <c r="G24" s="16" t="n">
         <v>0.05</v>
@@ -6060,16 +6063,16 @@
         <v>75</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G25" s="16" t="n">
         <v>0.05</v>
@@ -6089,16 +6092,16 @@
         <v>77</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G26" s="16" t="n">
         <v>0.03</v>
@@ -6118,16 +6121,16 @@
         <v>79</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G27" s="16" t="n">
         <v>0.04</v>
@@ -6147,16 +6150,16 @@
         <v>81</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D28" s="28" t="s">
         <v>59</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G28" s="29" t="n">
         <v>0.07</v>
@@ -6191,16 +6194,16 @@
         <v>85</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G30" s="16" t="n">
         <v>0.02</v>
@@ -6209,27 +6212,27 @@
         <v>0</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="14" t="s">
-        <v>88</v>
-      </c>
       <c r="C31" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>0.01</v>
@@ -6243,22 +6246,22 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>90</v>
-      </c>
       <c r="C32" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G32" s="16" t="n">
         <v>0.01</v>
@@ -6272,22 +6275,22 @@
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>92</v>
-      </c>
       <c r="C33" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G33" s="16" t="n">
         <v>0.02</v>
@@ -6301,22 +6304,22 @@
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="27" t="s">
-        <v>94</v>
-      </c>
       <c r="C34" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>34</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G34" s="29" t="n">
         <v>0.01</v>
@@ -6330,10 +6333,10 @@
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="25" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>96</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -6345,22 +6348,22 @@
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>98</v>
-      </c>
       <c r="C36" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G36" s="16" t="n">
         <v>0.02</v>
@@ -6374,22 +6377,22 @@
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>100</v>
-      </c>
       <c r="C37" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G37" s="16" t="n">
         <v>0.01</v>
@@ -6403,22 +6406,22 @@
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>102</v>
-      </c>
       <c r="C38" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G38" s="16" t="n">
         <v>0.02</v>
@@ -6432,22 +6435,22 @@
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="C39" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>105</v>
-      </c>
       <c r="E39" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>0.02</v>
@@ -6461,22 +6464,22 @@
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>107</v>
-      </c>
       <c r="C40" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G40" s="16" t="n">
         <v>0.01</v>
@@ -6490,22 +6493,22 @@
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="C41" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G41" s="16" t="n">
         <v>0.01</v>
@@ -6519,22 +6522,22 @@
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>111</v>
-      </c>
       <c r="C42" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G42" s="16" t="n">
         <v>0.01</v>
@@ -6548,22 +6551,22 @@
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="27" t="s">
-        <v>113</v>
-      </c>
       <c r="C43" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E43" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="28" t="s">
         <v>168</v>
-      </c>
-      <c r="F43" s="28" t="s">
-        <v>169</v>
       </c>
       <c r="G43" s="29" t="n">
         <v>0.01</v>
@@ -6577,7 +6580,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G45" s="31" t="n">
         <f aca="false">SUM(G7:G43)</f>
@@ -6590,7 +6593,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G46" s="21" t="str">
         <f aca="false">IF(ROUND(G45*100,2)=100,"OK","ERROR - weights total "&amp;TEXT(G45,"0.0%"))</f>
@@ -6599,12 +6602,12 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -6642,7 +6645,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6660,22 +6663,22 @@
         <v>24</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6683,7 +6686,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>1</v>
@@ -6696,13 +6699,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="H4" s="14" t="s">
         <v>183</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6710,7 +6713,7 @@
         <v>36</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>1</v>
@@ -6723,13 +6726,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="14" t="s">
         <v>187</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6737,7 +6740,7 @@
         <v>38</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>1</v>
@@ -6750,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G6" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>190</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6764,7 +6767,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>1</v>
@@ -6777,13 +6780,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G7" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" s="14" t="s">
         <v>193</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6791,7 +6794,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>0.05</v>
@@ -6804,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G8" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="H8" s="14" t="s">
         <v>196</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6818,7 +6821,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>0</v>
@@ -6831,13 +6834,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6845,7 +6848,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0</v>
@@ -6861,10 +6864,10 @@
         <v>49</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6872,7 +6875,7 @@
         <v>57</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>0</v>
@@ -6885,13 +6888,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G11" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="H11" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6912,13 +6915,13 @@
         <v>0.8</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G12" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H12" s="14" t="s">
         <v>205</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6939,13 +6942,13 @@
         <v>1</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G13" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="H13" s="14" t="s">
         <v>207</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6966,13 +6969,13 @@
         <v>1</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H14" s="14" t="s">
         <v>209</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6993,13 +6996,13 @@
         <v>0.15</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G15" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H15" s="14" t="s">
         <v>211</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7007,7 +7010,7 @@
         <v>80</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>0</v>
@@ -7023,10 +7026,10 @@
         <v>49</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7034,7 +7037,7 @@
         <v>84</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>0</v>
@@ -7047,10 +7050,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>86</v>
+        <v>215</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H17" s="14" t="s">
         <v>216</v>
@@ -7058,7 +7061,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>217</v>
@@ -7074,10 +7077,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H18" s="14" t="s">
         <v>218</v>
@@ -7085,7 +7088,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>219</v>
@@ -7104,7 +7107,7 @@
         <v>49</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>220</v>
@@ -7112,7 +7115,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>221</v>
@@ -7128,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>222</v>
@@ -7348,8 +7351,8 @@
       <c r="D8" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="E8" s="35" t="n">
-        <v>46248</v>
+      <c r="E8" s="35" t="s">
+        <v>253</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>240</v>
@@ -7362,15 +7365,15 @@
         <v>241</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C9" s="35" t="n">
         <v>46241</v>
@@ -7389,18 +7392,18 @@
         <v/>
       </c>
       <c r="H9" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C10" s="35" t="n">
         <v>46241</v>
@@ -7419,18 +7422,18 @@
         <v>6</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C11" s="35" t="n">
         <v>46241</v>
@@ -7449,22 +7452,22 @@
         <v>6</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C12" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E12" s="35" t="n">
         <v>46255</v>
@@ -7477,24 +7480,24 @@
         <v>6</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C13" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>46255</v>
@@ -7507,22 +7510,22 @@
         <v>6</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C14" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E14" s="35" t="n">
         <v>46252</v>
@@ -7538,15 +7541,15 @@
         <v>241</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C15" s="35" t="n">
         <v>46245</v>
@@ -7568,21 +7571,21 @@
         <v>241</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C16" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E16" s="35" t="n">
         <v>46247</v>
@@ -7595,24 +7598,24 @@
         <v>2</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C17" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E17" s="35" t="n">
         <v>46249</v>
@@ -7625,15 +7628,15 @@
         <v>2</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C19" s="30" t="n">
         <f aca="false">COUNTIF(F5:F17,"Open")</f>
@@ -7642,7 +7645,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C20" s="30" t="n">
         <f aca="false">COUNTIFS(F5:F17,"Open",H5:H17,"Critical")</f>
@@ -7651,7 +7654,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C21" s="30" t="n">
         <f aca="false">COUNTIF(F5:F17,"Closed")</f>

--- a/SVV_Balaji_Weekly_Project_Report.xlsx
+++ b/SVV_Balaji_Weekly_Project_Report.xlsx
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="298">
   <si>
     <t xml:space="preserve">SVV BALAJI - PROJECT GANTT CHART</t>
   </si>
   <si>
-    <t xml:space="preserve">Revised 11-Aug-2026 following client decisions on sales channel and GST. Week 1 commenced 04-Aug-2026. Amber bars are B2C activities added by Decision 1 and are conditional on written agreement of cost and timeline (action A-10). Red line marks the current reporting week.</t>
+    <t xml:space="preserve">Revised 19-Aug-2026. Week 1 commenced 04-Aug-2026. Amber bars are B2C activities added by Decision 1 and are conditional on written agreement of cost and timeline (action A-10). Red line marks the current reporting week. Start / Finish columns remain the agreed baseline (A-01) and are deliberately not moved when an activity finishes early - the bar shows the plan, the % Done column shows reality against it.</t>
   </si>
   <si>
     <t xml:space="preserve">04-Aug</t>
@@ -376,7 +376,7 @@
     <t xml:space="preserve">B2C scope - conditional on A-10 (cost &amp; timeline agreement)</t>
   </si>
   <si>
-    <t xml:space="preserve">Red vertical line = current reporting week (w/c 11-Aug-2026)</t>
+    <t xml:space="preserve">Red vertical line = current reporting week (w/c 18-Aug-2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Bars are formula-driven: edit the Start / Finish week columns and the chart updates automatically.</t>
@@ -388,7 +388,7 @@
     <t xml:space="preserve">Revised 11-Aug-2026. Decision 1 (both B2B and B2C sales channels with separate pricing) adds four activities beyond the signed scope of work: WS1.6, WS1.7, WS3.5 and WS5.8, plus activation of WS4.5.</t>
   </si>
   <si>
-    <t xml:space="preserve">Weeks are numbered from Week 1 commencing 04-Aug-2026. B2C activities extend the programme to Week 21 and are conditional on written agreement of cost and timeline (action A-10). The B2B launch remains at Week 18.</t>
+    <t xml:space="preserve">Weeks are numbered from Week 1 commencing 04-Aug-2026. B2C activities extend the programme to Week 21 and are conditional on written agreement of cost and timeline (action A-10). The B2B launch remains at Week 18. Planned start / finish weeks are the agreed baseline and are not revised when an activity delivers early; % Complete carries the actual position. Progress updated 19-Aug-2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Workstream / Activity</t>
@@ -544,7 +544,7 @@
     <t xml:space="preserve">Yellow rows are B2C activities added by Decision 1 - not in the signed scope of work.</t>
   </si>
   <si>
-    <t xml:space="preserve">WEEKLY PROGRESS REPORT - WEEK 2, UPDATED 14-AUG-2026</t>
+    <t xml:space="preserve">WEEKLY PROGRESS REPORT - WEEK 3, UPDATED 19-AUG-2026</t>
   </si>
   <si>
     <t xml:space="preserve">Planned % (this wk)</t>
@@ -610,16 +610,19 @@
     <t xml:space="preserve">Sales &amp; order fulfilment (B2B), dispatch &amp; delivery</t>
   </si>
   <si>
-    <t xml:space="preserve">Channel-aware order model in design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNBLOCKED 11-Aug by Decision 1. Building channel-aware from the start</t>
+    <t xml:space="preserve">Order model live end to end: draft, placement with re-pricing, confirmation, batch-wise allocation, pack, dispatch and delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-13 answered 16-Aug and built. Orders now hold a DRAFT state, finished-goods stock moves against the same movement ledger raw material has always used, and a cancelled order keeps its allocation rows marked released rather than deleting them. Dispatch and delivery timestamps added 19-Aug (see A-14) - without them no delivery-performance report is computable, and a timestamp cannot be backfilled. Remaining 20% is invoicing and the e-way bill hand-off, which wait on A-11.</t>
   </si>
   <si>
     <t xml:space="preserve">Channel pricing engine (B2B / B2C)</t>
   </si>
   <si>
-    <t xml:space="preserve">NEW activity from Decision 1. Dated price lists per channel</t>
+    <t xml:space="preserve">Live: dated price rules per channel and customer type, quantity breaks, supersede endpoint, resolve endpoint and a B2B/B2C comparison per product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete. A rate is never edited in place: superseding closes the current rule and opens a new one, so an invoice raised in June still reproduces June's price years later. Prices are frozen onto the order line at placement, not at draft, so a draft parked for a week cannot lock in a stale rate.</t>
   </si>
   <si>
     <t xml:space="preserve">Consumer (B2C) commerce APIs</t>
@@ -637,10 +640,10 @@
     <t xml:space="preserve">Complete. Also added the missing /auth/refresh, /auth/logout and /auth/me endpoints, without which no client could hold a session beyond 15 minutes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Live screens: branches, users, farmers (registration, approval, QR/barcode), agreements, seed distribution, training, field visits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Started 6 weeks early. All FRD 6-12 screens built and manually tested end to end. Remaining 20% is the product &amp; channel-pricing screens added by Decision 1.</t>
+    <t xml:space="preserve">Live screens: branches, users, farmers (registration, approval, QR/barcode), agreements, seed distribution, training, field visits, and multi-plot land profiling per farmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete - the outstanding product and channel-pricing screens landed with WS2.5. Land profiling added 16-Aug: a farmer can hold several plots, each with survey number, soil, irrigation, crop and GPS, and the plot now carries through harvest inspection into the collection and batch, so the consumer trace page resolves to a field rather than only to a farmer.</t>
   </si>
   <si>
     <t xml:space="preserve">Live screens: procurement plans, harvest inspections, collections, raw material batches with upstream trace, warehouses with per-unit occupancy, batch-wise stock (in/out/transfer/adjust) and the append-only movement ledger</t>
@@ -655,10 +658,25 @@
     <t xml:space="preserve">Complete - 8 weeks ahead of baseline. Panel is 22 of 25 screens. Recipe composition rules and quality gates are enforced in the forms, not discovered through server errors. Multigrain production live as of 14-Aug with a blend worksheet showing the required quantity per grain. Pending manual test.</t>
   </si>
   <si>
-    <t xml:space="preserve">Live screen: farm-to-fork trace - a finished-goods batch number resolves to the production run, recipe version, quality checks and the farmers behind it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traceability screen built early for client demonstration. Dashboards and MIS reports still to come.</t>
+    <t xml:space="preserve">Live screens: customers (one registry across both channels, with credit headroom per B2B account), price lists (dated rules, changed by superseding only), orders (draft through delivery, with the allocated batches shown as the picking slip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete - 9 weeks ahead of baseline. The admin panel is now 27 of 27 screens; nothing renders a placeholder. Channel is chosen at customer registration and cannot be changed afterwards, because it decides which price list every future order of theirs resolves against. Allocation is a server action rather than a form: it picks batches first-expiry-first-out from QA-released stock, which the panel could not do correctly on its own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live screen: farm-to-fork trace, now showing plot-level origin. FRD 34 audited line by line 19-Aug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traceability screen built early for client demonstration. Section 34 names roughly forty reports across nine families; thirty-five are answerable from data already captured. Five are not, and the audit is issued as SVV_Balaji_FRD34_Reporting_Gaps.md - one of the five (delivery timing) was closed immediately rather than raised, because a timestamp is the only kind of data that cannot be reconstructed later. The other three are questions for the client, tracked as A-14. Reporting module build starts once the current build passes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture Expert app (field visits, crop monitoring, training logs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installable app at /field with its own login and home-screen icon: today's schedule, farmer onboarding with land profiling, seed distribution, field visits, training sessions and the harvest inspection gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 15-16 Aug as a separate front end rather than a Flutter app - one codebase for validation rules, no app store, installs to the phone home screen from the browser. Camera capture and client-side image compression are in, so a 4 MB field photo uploads as roughly 380 KB over rural mobile data. Remaining 40% is offline capture: a service worker plus a queued write path, which is real work and is the only part of the original brief a website does not get for free.</t>
   </si>
   <si>
     <t xml:space="preserve">Consumer app / website (B2C)</t>
@@ -670,10 +688,10 @@
     <t xml:space="preserve">Cloud object storage</t>
   </si>
   <si>
-    <t xml:space="preserve">Blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Still awaiting Decision 3. More urgent now B2C is confirmed</t>
+    <t xml:space="preserve">Live: every photo and document in the system uploads through one interface - farmer KYC, inspection photos, field visit evidence, training materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No longer blocking. Interim account in use since 14-Aug, with credentials held only in the backend environment file and in no document, chart or repository file. Storage sits behind a single abstract class, so changing provider is one class and one line. A-04 remains open on ownership and permanence, not capability.</t>
   </si>
   <si>
     <t xml:space="preserve">GST e-invoicing &amp; e-way bill via GSP</t>
@@ -700,16 +718,16 @@
     <t xml:space="preserve">OVERALL PROJECT COMPLETION (weighted)</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend is running well ahead of baseline: WS2.1, WS2.3 and WS2.4 are complete and WS2.2 and WS2.6 are underway, between 4 and 8 weeks earlier than the proposed schedule. The admin panel now covers 22 of its 25 screens; only the sales screens (customers, price lists, orders) remain, and those are held pending A-13.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No activity is DELAYED. A-05 (multigrain) CLOSED 14-Aug - blended production is in scope, the feature flag has been removed and the blend ratio is now enforced at production time rather than only at recipe approval. WS4.1 remains blocked on Decision 3 (A-04). A-12 (pagination and response envelope) reached its 13-Aug target without landing; 22 panel screens absorb it through an adapter, so nothing is blocked, but the change is now larger than it was on 11-Aug.</t>
+    <t xml:space="preserve">Frontend is complete against the current scope and running well ahead of baseline. The admin panel is 27 of 27 screens - WS2.1 through WS2.5 all complete, between 4 and 9 weeks earlier than the proposed schedule - and the Agriculture Expert app is live as an installable field app. Role-based access was rebuilt on 16-Aug so a Super Admin can grant any page to any role from the panel without a redeploy; on a project where who does what will keep changing, that was a release cycle per administrative decision. Only WS2.6 (dashboards and reports) remains open in the panel workstream.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No activity is DELAYED. A-13 CLOSED 16-Aug and is built. A-14 raised 19-Aug covering three reporting inputs FRD 34 assumes and the system does not capture - production cost, machine utilisation and the credit-period start date; the fourth gap, delivery timing, was closed the same day rather than raised. A-12 (pagination and response envelope) is now 6 days past its target with no pagination DTO in the backend: all 27 panel screens absorb it through an adapter so nothing is blocked, but the movement ledger, production and quality lists grow monotonically and will be the first to become unusable on production data. A-04 remains open on storage ownership. A-10 and A-11 both passed their 18-Aug target and are now overdue.</t>
   </si>
   <si>
     <t xml:space="preserve">CONSOLIDATED ACTION TRACKER</t>
   </si>
   <si>
-    <t xml:space="preserve">Open actions remain on this tracker until formally closed. Ageing is calculated automatically from the date raised. A-02 and A-03 closed 11-Aug-2026; A-10 and A-11 raised the same day.</t>
+    <t xml:space="preserve">Open actions remain on this tracker until formally closed. Ageing is calculated automatically from the date raised. A-02 and A-03 closed 11-Aug-2026; A-05 closed 14-Aug; A-13 closed 16-Aug. A-14 raised 19-Aug-2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Ref</t>
@@ -868,7 +886,7 @@
     <t xml:space="preserve">Ujjawal / Raunak</t>
   </si>
   <si>
-    <t xml:space="preserve">Internal. Target date reached with no pagination DTO in the backend. 22 admin panel screens are now built against the unpaginated shape - an adapter absorbs the change, but the movement ledger, production and quality lists all grow monotonically and will be the first to become unusable on production data. Written proposal issued 11-Aug.</t>
+    <t xml:space="preserve">Internal. Target date reached 13-Aug with no pagination DTO in the backend, now 6 days overdue. All 27 admin panel screens are built against the unpaginated shape - an adapter absorbs the change, so this is still a non-breaking fix rather than a rework - but the movement ledger, production and quality lists all grow monotonically and will be the first to become unusable on production data. Written proposal issued 11-Aug.</t>
   </si>
   <si>
     <t xml:space="preserve">A-13</t>
@@ -877,7 +895,19 @@
     <t xml:space="preserve">Decide: order DRAFT state, finished-goods stock movement ledger, and allocation history retention on cancellation</t>
   </si>
   <si>
-    <t xml:space="preserve">Internal. Shapes the WS2.5 sales screens. Finished-goods stock currently has no audit trail, unlike raw material.</t>
+    <t xml:space="preserve">CLOSED 16-Aug-2026, all three answered yes and built. Orders now open in DRAFT, with the price resolved and frozen onto the line at placement rather than at draft - a draft parked for a week is placed at that week's rate, and any line that moved is shown back before the order commits. Finished-goods stock now writes to the same StockMovement ledger raw material has always used, rather than a second table. Cancelling an order marks its allocations released with a reason instead of deleting them, so "you reserved me that batch and then cancelled" has an answer in the data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm three reporting inputs FRD 34 assumes: per-batch production cost, what "machine utilisation" should measure, and the date a credit period runs from (SVV_Balaji_FRD34_Reporting_Gaps.md)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVV Balaji / Ujjawal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRD 34 names ~40 reports; 35 are answerable from data already captured. Five are not. Delivery timing was the fifth and has been closed unilaterally - dispatch and delivery timestamps were added 19-Aug, because a timestamp cannot be backfilled and every order shipped before the fix would have been permanently unmeasurable. The three remaining need a client answer: (1) production cost - nothing records what it costs to convert raw material, so Profit Analysis can only show gross margin over raw material; recommend one figure per batch at completion. (2) Machine utilisation - machine is free text with no run times, so no percentage is computable; recommend a machine master and run counts. (3) Credit period - CREDIT_30 has never been defined as 30 days from what, so "overdue" is not currently computable; recommend dispatch date. If unanswered, WS2.6 ships the 35 reports that have inputs and the rest name the missing field rather than showing an empty chart.</t>
   </si>
   <si>
     <t xml:space="preserve">Open actions:</t>
@@ -1029,7 +1059,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1040,6 +1070,15 @@
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
         <color rgb="FFCC0000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFC00000"/>
       </left>
       <right/>
       <top/>
@@ -1121,7 +1160,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1145,7 +1184,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1266,7 +1305,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -1705,8 +1744,8 @@
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
@@ -1752,11 +1791,11 @@
         <f aca="false">IF(AND($D7&lt;&gt;"",$E7&lt;&gt;"",H$5&gt;=$D7,H$5&lt;=$E7),IF($F7&gt;=1,3,IF($G7="Blocked",2,IF($G7="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
-      <c r="I7" s="18" t="str">
+      <c r="I7" s="17" t="str">
         <f aca="false">IF(AND($D7&lt;&gt;"",$E7&lt;&gt;"",I$5&gt;=$D7,I$5&lt;=$E7),IF($F7&gt;=1,3,IF($G7="Blocked",2,IF($G7="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J7" s="17" t="str">
+      <c r="J7" s="18" t="str">
         <f aca="false">IF(AND($D7&lt;&gt;"",$E7&lt;&gt;"",J$5&gt;=$D7,J$5&lt;=$E7),IF($F7&gt;=1,3,IF($G7="Blocked",2,IF($G7="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -1859,11 +1898,11 @@
         <f aca="false">IF(AND($D8&lt;&gt;"",$E8&lt;&gt;"",H$5&gt;=$D8,H$5&lt;=$E8),IF($F8&gt;=1,3,IF($G8="Blocked",2,IF($G8="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="17" t="n">
         <f aca="false">IF(AND($D8&lt;&gt;"",$E8&lt;&gt;"",I$5&gt;=$D8,I$5&lt;=$E8),IF($F8&gt;=1,3,IF($G8="Blocked",2,IF($G8="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
-      <c r="J8" s="17" t="str">
+      <c r="J8" s="18" t="str">
         <f aca="false">IF(AND($D8&lt;&gt;"",$E8&lt;&gt;"",J$5&gt;=$D8,J$5&lt;=$E8),IF($F8&gt;=1,3,IF($G8="Blocked",2,IF($G8="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -1966,11 +2005,11 @@
         <f aca="false">IF(AND($D9&lt;&gt;"",$E9&lt;&gt;"",H$5&gt;=$D9,H$5&lt;=$E9),IF($F9&gt;=1,3,IF($G9="Blocked",2,IF($G9="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="17" t="n">
         <f aca="false">IF(AND($D9&lt;&gt;"",$E9&lt;&gt;"",I$5&gt;=$D9,I$5&lt;=$E9),IF($F9&gt;=1,3,IF($G9="Blocked",2,IF($G9="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <f aca="false">IF(AND($D9&lt;&gt;"",$E9&lt;&gt;"",J$5&gt;=$D9,J$5&lt;=$E9),IF($F9&gt;=1,3,IF($G9="Blocked",2,IF($G9="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
@@ -2073,11 +2112,11 @@
         <f aca="false">IF(AND($D10&lt;&gt;"",$E10&lt;&gt;"",H$5&gt;=$D10,H$5&lt;=$E10),IF($F10&gt;=1,3,IF($G10="Blocked",2,IF($G10="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I10" s="18" t="str">
+      <c r="I10" s="17" t="str">
         <f aca="false">IF(AND($D10&lt;&gt;"",$E10&lt;&gt;"",I$5&gt;=$D10,I$5&lt;=$E10),IF($F10&gt;=1,3,IF($G10="Blocked",2,IF($G10="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <f aca="false">IF(AND($D10&lt;&gt;"",$E10&lt;&gt;"",J$5&gt;=$D10,J$5&lt;=$E10),IF($F10&gt;=1,3,IF($G10="Blocked",2,IF($G10="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
@@ -2171,7 +2210,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>44</v>
@@ -2180,11 +2219,11 @@
         <f aca="false">IF(AND($D11&lt;&gt;"",$E11&lt;&gt;"",H$5&gt;=$D11,H$5&lt;=$E11),IF($F11&gt;=1,3,IF($G11="Blocked",2,IF($G11="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="17" t="n">
         <f aca="false">IF(AND($D11&lt;&gt;"",$E11&lt;&gt;"",I$5&gt;=$D11,I$5&lt;=$E11),IF($F11&gt;=1,3,IF($G11="Blocked",2,IF($G11="Conditional",4,1))),"")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="18" t="n">
         <f aca="false">IF(AND($D11&lt;&gt;"",$E11&lt;&gt;"",J$5&gt;=$D11,J$5&lt;=$E11),IF($F11&gt;=1,3,IF($G11="Blocked",2,IF($G11="Conditional",4,1))),"")</f>
         <v>1</v>
       </c>
@@ -2278,22 +2317,22 @@
         <v>3</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H12" s="17" t="str">
         <f aca="false">IF(AND($D12&lt;&gt;"",$E12&lt;&gt;"",H$5&gt;=$D12,H$5&lt;=$E12),IF($F12&gt;=1,3,IF($G12="Blocked",2,IF($G12="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="17" t="n">
         <f aca="false">IF(AND($D12&lt;&gt;"",$E12&lt;&gt;"",I$5&gt;=$D12,I$5&lt;=$E12),IF($F12&gt;=1,3,IF($G12="Blocked",2,IF($G12="Conditional",4,1))),"")</f>
-        <v>1</v>
-      </c>
-      <c r="J12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="18" t="n">
         <f aca="false">IF(AND($D12&lt;&gt;"",$E12&lt;&gt;"",J$5&gt;=$D12,J$5&lt;=$E12),IF($F12&gt;=1,3,IF($G12="Blocked",2,IF($G12="Conditional",4,1))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="17" t="str">
         <f aca="false">IF(AND($D12&lt;&gt;"",$E12&lt;&gt;"",K$5&gt;=$D12,K$5&lt;=$E12),IF($F12&gt;=1,3,IF($G12="Blocked",2,IF($G12="Conditional",4,1))),"")</f>
@@ -2394,11 +2433,11 @@
         <f aca="false">IF(AND($D13&lt;&gt;"",$E13&lt;&gt;"",H$5&gt;=$D13,H$5&lt;=$E13),IF($F13&gt;=1,3,IF($G13="Blocked",2,IF($G13="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I13" s="18" t="str">
+      <c r="I13" s="17" t="str">
         <f aca="false">IF(AND($D13&lt;&gt;"",$E13&lt;&gt;"",I$5&gt;=$D13,I$5&lt;=$E13),IF($F13&gt;=1,3,IF($G13="Blocked",2,IF($G13="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J13" s="17" t="str">
+      <c r="J13" s="18" t="str">
         <f aca="false">IF(AND($D13&lt;&gt;"",$E13&lt;&gt;"",J$5&gt;=$D13,J$5&lt;=$E13),IF($F13&gt;=1,3,IF($G13="Blocked",2,IF($G13="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -2501,11 +2540,11 @@
         <f aca="false">IF(AND($D14&lt;&gt;"",$E14&lt;&gt;"",H$5&gt;=$D14,H$5&lt;=$E14),IF($F14&gt;=1,3,IF($G14="Blocked",2,IF($G14="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I14" s="18" t="str">
+      <c r="I14" s="17" t="str">
         <f aca="false">IF(AND($D14&lt;&gt;"",$E14&lt;&gt;"",I$5&gt;=$D14,I$5&lt;=$E14),IF($F14&gt;=1,3,IF($G14="Blocked",2,IF($G14="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J14" s="17" t="str">
+      <c r="J14" s="18" t="str">
         <f aca="false">IF(AND($D14&lt;&gt;"",$E14&lt;&gt;"",J$5&gt;=$D14,J$5&lt;=$E14),IF($F14&gt;=1,3,IF($G14="Blocked",2,IF($G14="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -2608,11 +2647,11 @@
         <f aca="false">IF(AND($D15&lt;&gt;"",$E15&lt;&gt;"",H$5&gt;=$D15,H$5&lt;=$E15),IF($F15&gt;=1,3,IF($G15="Blocked",2,IF($G15="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I15" s="18" t="str">
+      <c r="I15" s="17" t="str">
         <f aca="false">IF(AND($D15&lt;&gt;"",$E15&lt;&gt;"",I$5&gt;=$D15,I$5&lt;=$E15),IF($F15&gt;=1,3,IF($G15="Blocked",2,IF($G15="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J15" s="17" t="str">
+      <c r="J15" s="18" t="str">
         <f aca="false">IF(AND($D15&lt;&gt;"",$E15&lt;&gt;"",J$5&gt;=$D15,J$5&lt;=$E15),IF($F15&gt;=1,3,IF($G15="Blocked",2,IF($G15="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -2702,8 +2741,8 @@
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
@@ -2749,11 +2788,11 @@
         <f aca="false">IF(AND($D17&lt;&gt;"",$E17&lt;&gt;"",H$5&gt;=$D17,H$5&lt;=$E17),IF($F17&gt;=1,3,IF($G17="Blocked",2,IF($G17="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="17" t="n">
         <f aca="false">IF(AND($D17&lt;&gt;"",$E17&lt;&gt;"",I$5&gt;=$D17,I$5&lt;=$E17),IF($F17&gt;=1,3,IF($G17="Blocked",2,IF($G17="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="18" t="n">
         <f aca="false">IF(AND($D17&lt;&gt;"",$E17&lt;&gt;"",J$5&gt;=$D17,J$5&lt;=$E17),IF($F17&gt;=1,3,IF($G17="Blocked",2,IF($G17="Conditional",4,1))),"")</f>
         <v>3</v>
       </c>
@@ -2847,34 +2886,34 @@
         <v>6</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H18" s="17" t="str">
         <f aca="false">IF(AND($D18&lt;&gt;"",$E18&lt;&gt;"",H$5&gt;=$D18,H$5&lt;=$E18),IF($F18&gt;=1,3,IF($G18="Blocked",2,IF($G18="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I18" s="18" t="str">
+      <c r="I18" s="17" t="str">
         <f aca="false">IF(AND($D18&lt;&gt;"",$E18&lt;&gt;"",I$5&gt;=$D18,I$5&lt;=$E18),IF($F18&gt;=1,3,IF($G18="Blocked",2,IF($G18="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J18" s="17" t="str">
+      <c r="J18" s="18" t="str">
         <f aca="false">IF(AND($D18&lt;&gt;"",$E18&lt;&gt;"",J$5&gt;=$D18,J$5&lt;=$E18),IF($F18&gt;=1,3,IF($G18="Blocked",2,IF($G18="Conditional",4,1))),"")</f>
         <v/>
       </c>
       <c r="K18" s="17" t="n">
         <f aca="false">IF(AND($D18&lt;&gt;"",$E18&lt;&gt;"",K$5&gt;=$D18,K$5&lt;=$E18),IF($F18&gt;=1,3,IF($G18="Blocked",2,IF($G18="Conditional",4,1))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" s="17" t="n">
         <f aca="false">IF(AND($D18&lt;&gt;"",$E18&lt;&gt;"",L$5&gt;=$D18,L$5&lt;=$E18),IF($F18&gt;=1,3,IF($G18="Blocked",2,IF($G18="Conditional",4,1))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" s="17" t="n">
         <f aca="false">IF(AND($D18&lt;&gt;"",$E18&lt;&gt;"",M$5&gt;=$D18,M$5&lt;=$E18),IF($F18&gt;=1,3,IF($G18="Blocked",2,IF($G18="Conditional",4,1))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N18" s="17" t="str">
         <f aca="false">IF(AND($D18&lt;&gt;"",$E18&lt;&gt;"",N$5&gt;=$D18,N$5&lt;=$E18),IF($F18&gt;=1,3,IF($G18="Blocked",2,IF($G18="Conditional",4,1))),"")</f>
@@ -2963,11 +3002,11 @@
         <f aca="false">IF(AND($D19&lt;&gt;"",$E19&lt;&gt;"",H$5&gt;=$D19,H$5&lt;=$E19),IF($F19&gt;=1,3,IF($G19="Blocked",2,IF($G19="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I19" s="18" t="str">
+      <c r="I19" s="17" t="str">
         <f aca="false">IF(AND($D19&lt;&gt;"",$E19&lt;&gt;"",I$5&gt;=$D19,I$5&lt;=$E19),IF($F19&gt;=1,3,IF($G19="Blocked",2,IF($G19="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J19" s="17" t="str">
+      <c r="J19" s="18" t="str">
         <f aca="false">IF(AND($D19&lt;&gt;"",$E19&lt;&gt;"",J$5&gt;=$D19,J$5&lt;=$E19),IF($F19&gt;=1,3,IF($G19="Blocked",2,IF($G19="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3070,11 +3109,11 @@
         <f aca="false">IF(AND($D20&lt;&gt;"",$E20&lt;&gt;"",H$5&gt;=$D20,H$5&lt;=$E20),IF($F20&gt;=1,3,IF($G20="Blocked",2,IF($G20="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I20" s="18" t="str">
+      <c r="I20" s="17" t="str">
         <f aca="false">IF(AND($D20&lt;&gt;"",$E20&lt;&gt;"",I$5&gt;=$D20,I$5&lt;=$E20),IF($F20&gt;=1,3,IF($G20="Blocked",2,IF($G20="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J20" s="17" t="str">
+      <c r="J20" s="18" t="str">
         <f aca="false">IF(AND($D20&lt;&gt;"",$E20&lt;&gt;"",J$5&gt;=$D20,J$5&lt;=$E20),IF($F20&gt;=1,3,IF($G20="Blocked",2,IF($G20="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3168,20 +3207,20 @@
         <v>12</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H21" s="17" t="str">
         <f aca="false">IF(AND($D21&lt;&gt;"",$E21&lt;&gt;"",H$5&gt;=$D21,H$5&lt;=$E21),IF($F21&gt;=1,3,IF($G21="Blocked",2,IF($G21="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I21" s="18" t="str">
+      <c r="I21" s="17" t="str">
         <f aca="false">IF(AND($D21&lt;&gt;"",$E21&lt;&gt;"",I$5&gt;=$D21,I$5&lt;=$E21),IF($F21&gt;=1,3,IF($G21="Blocked",2,IF($G21="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J21" s="17" t="str">
+      <c r="J21" s="18" t="str">
         <f aca="false">IF(AND($D21&lt;&gt;"",$E21&lt;&gt;"",J$5&gt;=$D21,J$5&lt;=$E21),IF($F21&gt;=1,3,IF($G21="Blocked",2,IF($G21="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3211,15 +3250,15 @@
       </c>
       <c r="Q21" s="17" t="n">
         <f aca="false">IF(AND($D21&lt;&gt;"",$E21&lt;&gt;"",Q$5&gt;=$D21,Q$5&lt;=$E21),IF($F21&gt;=1,3,IF($G21="Blocked",2,IF($G21="Conditional",4,1))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R21" s="17" t="n">
         <f aca="false">IF(AND($D21&lt;&gt;"",$E21&lt;&gt;"",R$5&gt;=$D21,R$5&lt;=$E21),IF($F21&gt;=1,3,IF($G21="Blocked",2,IF($G21="Conditional",4,1))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S21" s="17" t="n">
         <f aca="false">IF(AND($D21&lt;&gt;"",$E21&lt;&gt;"",S$5&gt;=$D21,S$5&lt;=$E21),IF($F21&gt;=1,3,IF($G21="Blocked",2,IF($G21="Conditional",4,1))),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T21" s="17" t="str">
         <f aca="false">IF(AND($D21&lt;&gt;"",$E21&lt;&gt;"",T$5&gt;=$D21,T$5&lt;=$E21),IF($F21&gt;=1,3,IF($G21="Blocked",2,IF($G21="Conditional",4,1))),"")</f>
@@ -3275,7 +3314,7 @@
         <v>13</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G22" s="15" t="s">
         <v>44</v>
@@ -3284,11 +3323,11 @@
         <f aca="false">IF(AND($D22&lt;&gt;"",$E22&lt;&gt;"",H$5&gt;=$D22,H$5&lt;=$E22),IF($F22&gt;=1,3,IF($G22="Blocked",2,IF($G22="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I22" s="18" t="str">
+      <c r="I22" s="17" t="str">
         <f aca="false">IF(AND($D22&lt;&gt;"",$E22&lt;&gt;"",I$5&gt;=$D22,I$5&lt;=$E22),IF($F22&gt;=1,3,IF($G22="Blocked",2,IF($G22="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J22" s="17" t="str">
+      <c r="J22" s="18" t="str">
         <f aca="false">IF(AND($D22&lt;&gt;"",$E22&lt;&gt;"",J$5&gt;=$D22,J$5&lt;=$E22),IF($F22&gt;=1,3,IF($G22="Blocked",2,IF($G22="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3378,8 +3417,8 @@
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
@@ -3416,20 +3455,20 @@
         <v>12</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H24" s="17" t="str">
         <f aca="false">IF(AND($D24&lt;&gt;"",$E24&lt;&gt;"",H$5&gt;=$D24,H$5&lt;=$E24),IF($F24&gt;=1,3,IF($G24="Blocked",2,IF($G24="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I24" s="18" t="str">
+      <c r="I24" s="17" t="str">
         <f aca="false">IF(AND($D24&lt;&gt;"",$E24&lt;&gt;"",I$5&gt;=$D24,I$5&lt;=$E24),IF($F24&gt;=1,3,IF($G24="Blocked",2,IF($G24="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J24" s="17" t="str">
+      <c r="J24" s="18" t="str">
         <f aca="false">IF(AND($D24&lt;&gt;"",$E24&lt;&gt;"",J$5&gt;=$D24,J$5&lt;=$E24),IF($F24&gt;=1,3,IF($G24="Blocked",2,IF($G24="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3532,11 +3571,11 @@
         <f aca="false">IF(AND($D25&lt;&gt;"",$E25&lt;&gt;"",H$5&gt;=$D25,H$5&lt;=$E25),IF($F25&gt;=1,3,IF($G25="Blocked",2,IF($G25="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I25" s="18" t="str">
+      <c r="I25" s="17" t="str">
         <f aca="false">IF(AND($D25&lt;&gt;"",$E25&lt;&gt;"",I$5&gt;=$D25,I$5&lt;=$E25),IF($F25&gt;=1,3,IF($G25="Blocked",2,IF($G25="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J25" s="17" t="str">
+      <c r="J25" s="18" t="str">
         <f aca="false">IF(AND($D25&lt;&gt;"",$E25&lt;&gt;"",J$5&gt;=$D25,J$5&lt;=$E25),IF($F25&gt;=1,3,IF($G25="Blocked",2,IF($G25="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3639,11 +3678,11 @@
         <f aca="false">IF(AND($D26&lt;&gt;"",$E26&lt;&gt;"",H$5&gt;=$D26,H$5&lt;=$E26),IF($F26&gt;=1,3,IF($G26="Blocked",2,IF($G26="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I26" s="18" t="str">
+      <c r="I26" s="17" t="str">
         <f aca="false">IF(AND($D26&lt;&gt;"",$E26&lt;&gt;"",I$5&gt;=$D26,I$5&lt;=$E26),IF($F26&gt;=1,3,IF($G26="Blocked",2,IF($G26="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J26" s="17" t="str">
+      <c r="J26" s="18" t="str">
         <f aca="false">IF(AND($D26&lt;&gt;"",$E26&lt;&gt;"",J$5&gt;=$D26,J$5&lt;=$E26),IF($F26&gt;=1,3,IF($G26="Blocked",2,IF($G26="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3746,11 +3785,11 @@
         <f aca="false">IF(AND($D27&lt;&gt;"",$E27&lt;&gt;"",H$5&gt;=$D27,H$5&lt;=$E27),IF($F27&gt;=1,3,IF($G27="Blocked",2,IF($G27="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I27" s="18" t="str">
+      <c r="I27" s="17" t="str">
         <f aca="false">IF(AND($D27&lt;&gt;"",$E27&lt;&gt;"",I$5&gt;=$D27,I$5&lt;=$E27),IF($F27&gt;=1,3,IF($G27="Blocked",2,IF($G27="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J27" s="17" t="str">
+      <c r="J27" s="18" t="str">
         <f aca="false">IF(AND($D27&lt;&gt;"",$E27&lt;&gt;"",J$5&gt;=$D27,J$5&lt;=$E27),IF($F27&gt;=1,3,IF($G27="Blocked",2,IF($G27="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3853,11 +3892,11 @@
         <f aca="false">IF(AND($D28&lt;&gt;"",$E28&lt;&gt;"",H$5&gt;=$D28,H$5&lt;=$E28),IF($F28&gt;=1,3,IF($G28="Blocked",2,IF($G28="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I28" s="18" t="str">
+      <c r="I28" s="17" t="str">
         <f aca="false">IF(AND($D28&lt;&gt;"",$E28&lt;&gt;"",I$5&gt;=$D28,I$5&lt;=$E28),IF($F28&gt;=1,3,IF($G28="Blocked",2,IF($G28="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J28" s="17" t="str">
+      <c r="J28" s="18" t="str">
         <f aca="false">IF(AND($D28&lt;&gt;"",$E28&lt;&gt;"",J$5&gt;=$D28,J$5&lt;=$E28),IF($F28&gt;=1,3,IF($G28="Blocked",2,IF($G28="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -3947,8 +3986,8 @@
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="12"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
@@ -3985,7 +4024,7 @@
         <v>6</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G30" s="15" t="s">
         <v>44</v>
@@ -3994,11 +4033,11 @@
         <f aca="false">IF(AND($D30&lt;&gt;"",$E30&lt;&gt;"",H$5&gt;=$D30,H$5&lt;=$E30),IF($F30&gt;=1,3,IF($G30="Blocked",2,IF($G30="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I30" s="18" t="str">
+      <c r="I30" s="17" t="str">
         <f aca="false">IF(AND($D30&lt;&gt;"",$E30&lt;&gt;"",I$5&gt;=$D30,I$5&lt;=$E30),IF($F30&gt;=1,3,IF($G30="Blocked",2,IF($G30="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J30" s="17" t="str">
+      <c r="J30" s="18" t="str">
         <f aca="false">IF(AND($D30&lt;&gt;"",$E30&lt;&gt;"",J$5&gt;=$D30,J$5&lt;=$E30),IF($F30&gt;=1,3,IF($G30="Blocked",2,IF($G30="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -4101,11 +4140,11 @@
         <f aca="false">IF(AND($D31&lt;&gt;"",$E31&lt;&gt;"",H$5&gt;=$D31,H$5&lt;=$E31),IF($F31&gt;=1,3,IF($G31="Blocked",2,IF($G31="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I31" s="18" t="str">
+      <c r="I31" s="17" t="str">
         <f aca="false">IF(AND($D31&lt;&gt;"",$E31&lt;&gt;"",I$5&gt;=$D31,I$5&lt;=$E31),IF($F31&gt;=1,3,IF($G31="Blocked",2,IF($G31="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J31" s="17" t="str">
+      <c r="J31" s="18" t="str">
         <f aca="false">IF(AND($D31&lt;&gt;"",$E31&lt;&gt;"",J$5&gt;=$D31,J$5&lt;=$E31),IF($F31&gt;=1,3,IF($G31="Blocked",2,IF($G31="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -4208,11 +4247,11 @@
         <f aca="false">IF(AND($D32&lt;&gt;"",$E32&lt;&gt;"",H$5&gt;=$D32,H$5&lt;=$E32),IF($F32&gt;=1,3,IF($G32="Blocked",2,IF($G32="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18" t="str">
+      <c r="I32" s="17" t="str">
         <f aca="false">IF(AND($D32&lt;&gt;"",$E32&lt;&gt;"",I$5&gt;=$D32,I$5&lt;=$E32),IF($F32&gt;=1,3,IF($G32="Blocked",2,IF($G32="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J32" s="17" t="str">
+      <c r="J32" s="18" t="str">
         <f aca="false">IF(AND($D32&lt;&gt;"",$E32&lt;&gt;"",J$5&gt;=$D32,J$5&lt;=$E32),IF($F32&gt;=1,3,IF($G32="Blocked",2,IF($G32="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -4315,11 +4354,11 @@
         <f aca="false">IF(AND($D33&lt;&gt;"",$E33&lt;&gt;"",H$5&gt;=$D33,H$5&lt;=$E33),IF($F33&gt;=1,3,IF($G33="Blocked",2,IF($G33="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18" t="str">
+      <c r="I33" s="17" t="str">
         <f aca="false">IF(AND($D33&lt;&gt;"",$E33&lt;&gt;"",I$5&gt;=$D33,I$5&lt;=$E33),IF($F33&gt;=1,3,IF($G33="Blocked",2,IF($G33="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J33" s="17" t="str">
+      <c r="J33" s="18" t="str">
         <f aca="false">IF(AND($D33&lt;&gt;"",$E33&lt;&gt;"",J$5&gt;=$D33,J$5&lt;=$E33),IF($F33&gt;=1,3,IF($G33="Blocked",2,IF($G33="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -4422,11 +4461,11 @@
         <f aca="false">IF(AND($D34&lt;&gt;"",$E34&lt;&gt;"",H$5&gt;=$D34,H$5&lt;=$E34),IF($F34&gt;=1,3,IF($G34="Blocked",2,IF($G34="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18" t="str">
+      <c r="I34" s="17" t="str">
         <f aca="false">IF(AND($D34&lt;&gt;"",$E34&lt;&gt;"",I$5&gt;=$D34,I$5&lt;=$E34),IF($F34&gt;=1,3,IF($G34="Blocked",2,IF($G34="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J34" s="17" t="str">
+      <c r="J34" s="18" t="str">
         <f aca="false">IF(AND($D34&lt;&gt;"",$E34&lt;&gt;"",J$5&gt;=$D34,J$5&lt;=$E34),IF($F34&gt;=1,3,IF($G34="Blocked",2,IF($G34="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -4516,8 +4555,8 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="12"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
@@ -4563,11 +4602,11 @@
         <f aca="false">IF(AND($D36&lt;&gt;"",$E36&lt;&gt;"",H$5&gt;=$D36,H$5&lt;=$E36),IF($F36&gt;=1,3,IF($G36="Blocked",2,IF($G36="Conditional",4,1))),"")</f>
         <v>1</v>
       </c>
-      <c r="I36" s="18" t="n">
+      <c r="I36" s="17" t="n">
         <f aca="false">IF(AND($D36&lt;&gt;"",$E36&lt;&gt;"",I$5&gt;=$D36,I$5&lt;=$E36),IF($F36&gt;=1,3,IF($G36="Blocked",2,IF($G36="Conditional",4,1))),"")</f>
         <v>1</v>
       </c>
-      <c r="J36" s="17" t="n">
+      <c r="J36" s="18" t="n">
         <f aca="false">IF(AND($D36&lt;&gt;"",$E36&lt;&gt;"",J$5&gt;=$D36,J$5&lt;=$E36),IF($F36&gt;=1,3,IF($G36="Blocked",2,IF($G36="Conditional",4,1))),"")</f>
         <v>1</v>
       </c>
@@ -4670,11 +4709,11 @@
         <f aca="false">IF(AND($D37&lt;&gt;"",$E37&lt;&gt;"",H$5&gt;=$D37,H$5&lt;=$E37),IF($F37&gt;=1,3,IF($G37="Blocked",2,IF($G37="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I37" s="18" t="n">
+      <c r="I37" s="17" t="n">
         <f aca="false">IF(AND($D37&lt;&gt;"",$E37&lt;&gt;"",I$5&gt;=$D37,I$5&lt;=$E37),IF($F37&gt;=1,3,IF($G37="Blocked",2,IF($G37="Conditional",4,1))),"")</f>
         <v>1</v>
       </c>
-      <c r="J37" s="17" t="n">
+      <c r="J37" s="18" t="n">
         <f aca="false">IF(AND($D37&lt;&gt;"",$E37&lt;&gt;"",J$5&gt;=$D37,J$5&lt;=$E37),IF($F37&gt;=1,3,IF($G37="Blocked",2,IF($G37="Conditional",4,1))),"")</f>
         <v>1</v>
       </c>
@@ -4777,11 +4816,11 @@
         <f aca="false">IF(AND($D38&lt;&gt;"",$E38&lt;&gt;"",H$5&gt;=$D38,H$5&lt;=$E38),IF($F38&gt;=1,3,IF($G38="Blocked",2,IF($G38="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I38" s="18" t="str">
+      <c r="I38" s="17" t="str">
         <f aca="false">IF(AND($D38&lt;&gt;"",$E38&lt;&gt;"",I$5&gt;=$D38,I$5&lt;=$E38),IF($F38&gt;=1,3,IF($G38="Blocked",2,IF($G38="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J38" s="17" t="str">
+      <c r="J38" s="18" t="str">
         <f aca="false">IF(AND($D38&lt;&gt;"",$E38&lt;&gt;"",J$5&gt;=$D38,J$5&lt;=$E38),IF($F38&gt;=1,3,IF($G38="Blocked",2,IF($G38="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -4884,11 +4923,11 @@
         <f aca="false">IF(AND($D39&lt;&gt;"",$E39&lt;&gt;"",H$5&gt;=$D39,H$5&lt;=$E39),IF($F39&gt;=1,3,IF($G39="Blocked",2,IF($G39="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I39" s="18" t="str">
+      <c r="I39" s="17" t="str">
         <f aca="false">IF(AND($D39&lt;&gt;"",$E39&lt;&gt;"",I$5&gt;=$D39,I$5&lt;=$E39),IF($F39&gt;=1,3,IF($G39="Blocked",2,IF($G39="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J39" s="17" t="str">
+      <c r="J39" s="18" t="str">
         <f aca="false">IF(AND($D39&lt;&gt;"",$E39&lt;&gt;"",J$5&gt;=$D39,J$5&lt;=$E39),IF($F39&gt;=1,3,IF($G39="Blocked",2,IF($G39="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -4991,11 +5030,11 @@
         <f aca="false">IF(AND($D40&lt;&gt;"",$E40&lt;&gt;"",H$5&gt;=$D40,H$5&lt;=$E40),IF($F40&gt;=1,3,IF($G40="Blocked",2,IF($G40="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I40" s="18" t="str">
+      <c r="I40" s="17" t="str">
         <f aca="false">IF(AND($D40&lt;&gt;"",$E40&lt;&gt;"",I$5&gt;=$D40,I$5&lt;=$E40),IF($F40&gt;=1,3,IF($G40="Blocked",2,IF($G40="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J40" s="17" t="str">
+      <c r="J40" s="18" t="str">
         <f aca="false">IF(AND($D40&lt;&gt;"",$E40&lt;&gt;"",J$5&gt;=$D40,J$5&lt;=$E40),IF($F40&gt;=1,3,IF($G40="Blocked",2,IF($G40="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -5098,11 +5137,11 @@
         <f aca="false">IF(AND($D41&lt;&gt;"",$E41&lt;&gt;"",H$5&gt;=$D41,H$5&lt;=$E41),IF($F41&gt;=1,3,IF($G41="Blocked",2,IF($G41="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I41" s="18" t="str">
+      <c r="I41" s="17" t="str">
         <f aca="false">IF(AND($D41&lt;&gt;"",$E41&lt;&gt;"",I$5&gt;=$D41,I$5&lt;=$E41),IF($F41&gt;=1,3,IF($G41="Blocked",2,IF($G41="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J41" s="17" t="str">
+      <c r="J41" s="18" t="str">
         <f aca="false">IF(AND($D41&lt;&gt;"",$E41&lt;&gt;"",J$5&gt;=$D41,J$5&lt;=$E41),IF($F41&gt;=1,3,IF($G41="Blocked",2,IF($G41="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -5205,11 +5244,11 @@
         <f aca="false">IF(AND($D42&lt;&gt;"",$E42&lt;&gt;"",H$5&gt;=$D42,H$5&lt;=$E42),IF($F42&gt;=1,3,IF($G42="Blocked",2,IF($G42="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I42" s="18" t="str">
+      <c r="I42" s="17" t="str">
         <f aca="false">IF(AND($D42&lt;&gt;"",$E42&lt;&gt;"",I$5&gt;=$D42,I$5&lt;=$E42),IF($F42&gt;=1,3,IF($G42="Blocked",2,IF($G42="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J42" s="17" t="str">
+      <c r="J42" s="18" t="str">
         <f aca="false">IF(AND($D42&lt;&gt;"",$E42&lt;&gt;"",J$5&gt;=$D42,J$5&lt;=$E42),IF($F42&gt;=1,3,IF($G42="Blocked",2,IF($G42="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -5312,11 +5351,11 @@
         <f aca="false">IF(AND($D43&lt;&gt;"",$E43&lt;&gt;"",H$5&gt;=$D43,H$5&lt;=$E43),IF($F43&gt;=1,3,IF($G43="Blocked",2,IF($G43="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="I43" s="18" t="str">
+      <c r="I43" s="17" t="str">
         <f aca="false">IF(AND($D43&lt;&gt;"",$E43&lt;&gt;"",I$5&gt;=$D43,I$5&lt;=$E43),IF($F43&gt;=1,3,IF($G43="Blocked",2,IF($G43="Conditional",4,1))),"")</f>
         <v/>
       </c>
-      <c r="J43" s="17" t="str">
+      <c r="J43" s="18" t="str">
         <f aca="false">IF(AND($D43&lt;&gt;"",$E43&lt;&gt;"",J$5&gt;=$D43,J$5&lt;=$E43),IF($F43&gt;=1,3,IF($G43="Blocked",2,IF($G43="Conditional",4,1))),"")</f>
         <v/>
       </c>
@@ -5700,7 +5739,7 @@
         <v>0.06</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>44</v>
@@ -5729,10 +5768,10 @@
         <v>0.02</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5889,10 +5928,10 @@
         <v>0.05</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5976,10 +6015,10 @@
         <v>0.03</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6005,7 +6044,7 @@
         <v>0.03</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>44</v>
@@ -6049,10 +6088,10 @@
         <v>0.05</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6209,7 +6248,7 @@
         <v>0.02</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>44</v>
@@ -6588,7 +6627,7 @@
       </c>
       <c r="H45" s="32" t="n">
         <f aca="false">SUMPRODUCT(G7:G43,H7:H43)</f>
-        <v>0.3565</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6631,7 +6670,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -6800,14 +6839,14 @@
         <v>0.05</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="E8" s="16" t="n">
         <f aca="false">D8-C8</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>195</v>
@@ -6827,20 +6866,20 @@
         <v>0</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="16" t="n">
         <f aca="false">D9-C9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6848,7 +6887,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0</v>
@@ -6867,7 +6906,7 @@
         <v>164</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6875,7 +6914,7 @@
         <v>57</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>0</v>
@@ -6891,10 +6930,10 @@
         <v>185</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6908,20 +6947,20 @@
         <v>0</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" s="16" t="n">
         <f aca="false">D12-C12</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>185</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6945,10 +6984,10 @@
         <v>185</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6972,99 +7011,99 @@
         <v>185</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">D15-C15</f>
-        <v>0.15</v>
-      </c>
-      <c r="F15" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="33" t="s">
         <v>185</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>212</v>
+        <v>69</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">D16-C16</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>49</v>
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">D17-C17</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>215</v>
+        <v>0.6</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>185</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>0</v>
@@ -7076,88 +7115,142 @@
         <f aca="false">D18-C18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>181</v>
+      <c r="F18" s="28" t="s">
+        <v>49</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>164</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">D19-C19</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>49</v>
+        <v>0.8</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>44</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">D20-C20</f>
         <v>0</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <f aca="false">D21-C21</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <f aca="false">D22-C22</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="D22" s="32" t="n">
+      <c r="G22" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="D24" s="32" t="n">
         <f aca="false">'2. Schedule Baseline'!H45</f>
-        <v>0.3565</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="21" t="s">
-        <v>226</v>
+        <v>0.509</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="21" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="21" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -7195,7 +7288,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7208,7 +7301,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7221,247 +7314,247 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C5" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E5" s="35" t="n">
         <v>46248</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G5" s="15" t="n">
         <f aca="true">IF(F5="Closed","",TODAY()-C5)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C6" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E6" s="35" t="n">
         <v>46246</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="G6" s="15" t="str">
         <f aca="true">IF(F6="Closed","",TODAY()-C6)</f>
         <v/>
       </c>
       <c r="H6" s="15" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C7" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E7" s="35" t="n">
         <v>46248</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="G7" s="15" t="str">
         <f aca="true">IF(F7="Closed","",TODAY()-C7)</f>
         <v/>
       </c>
       <c r="H7" s="15" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C8" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G8" s="15" t="n">
         <f aca="true">IF(F8="Closed","",TODAY()-C8)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C9" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E9" s="35" t="n">
         <v>46248</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="G9" s="15" t="str">
         <f aca="true">IF(F9="Closed","",TODAY()-C9)</f>
         <v/>
       </c>
       <c r="H9" s="15" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C10" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E10" s="35" t="n">
         <v>46262</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G10" s="15" t="n">
         <f aca="true">IF(F10="Closed","",TODAY()-C10)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C11" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E11" s="35" t="n">
         <v>46262</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G11" s="15" t="n">
         <f aca="true">IF(F11="Closed","",TODAY()-C11)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="I11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C12" s="35" t="n">
         <v>46241</v>
@@ -7473,192 +7566,222 @@
         <v>46255</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G12" s="15" t="n">
         <f aca="true">IF(F12="Closed","",TODAY()-C12)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C13" s="35" t="n">
         <v>46241</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>46255</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G13" s="15" t="n">
         <f aca="true">IF(F13="Closed","",TODAY()-C13)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="I13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C14" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E14" s="35" t="n">
         <v>46252</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G14" s="15" t="n">
         <f aca="true">IF(F14="Closed","",TODAY()-C14)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C15" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E15" s="35" t="n">
         <v>46252</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G15" s="15" t="n">
         <f aca="true">IF(F15="Closed","",TODAY()-C15)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C16" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E16" s="35" t="n">
         <v>46247</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="true">IF(F16="Closed","",TODAY()-C16)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C17" s="35" t="n">
         <v>46245</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E17" s="35" t="n">
         <v>46249</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="G17" s="15" t="n">
+        <v>251</v>
+      </c>
+      <c r="G17" s="15" t="str">
         <f aca="true">IF(F17="Closed","",TODAY()-C17)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="H17" s="34" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" s="35" t="n">
+        <v>46253</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>46260</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <f aca="true">IF(F18="Closed","",TODAY()-C18)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="30" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C19" s="30" t="n">
-        <f aca="false">COUNTIF(F5:F17,"Open")</f>
+        <f aca="false">COUNTIF(F5:F18,"Open")</f>
         <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="30" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C20" s="30" t="n">
-        <f aca="false">COUNTIFS(F5:F17,"Open",H5:H17,"Critical")</f>
+        <f aca="false">COUNTIFS(F5:F18,"Open",H5:H18,"Critical")</f>
         <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="30" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C21" s="30" t="n">
-        <f aca="false">COUNTIF(F5:F17,"Closed")</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(F5:F18,"Closed")</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
